--- a/branches/ci/gh-pages-preview/ValueSet-mii-vs-kardio-gewichtsveraenderung-snomedct.xlsx
+++ b/branches/ci/gh-pages-preview/ValueSet-mii-vs-kardio-gewichtsveraenderung-snomedct.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>
